--- a/data/processed/quality/lottery_quality_report.xlsx
+++ b/data/processed/quality/lottery_quality_report.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12703</v>
+        <v>12709</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-23 08:14:23</t>
+          <t>2026-05-24 05:27:04</t>
         </is>
       </c>
     </row>
@@ -578,16 +578,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2624</v>
+        <v>2625</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>43534</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="G2" t="n">
-        <v>2624</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="3">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2592</v>
+        <v>2593</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>36596</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>46162</v>
+        <v>46165</v>
       </c>
       <c r="G3" t="n">
-        <v>2592</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="4">
@@ -636,16 +636,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2287</v>
+        <v>2288</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>37951</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>46162</v>
+        <v>46165</v>
       </c>
       <c r="G4" t="n">
-        <v>2287</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="5">
@@ -665,16 +665,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>42949</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46162</v>
+        <v>46165</v>
       </c>
       <c r="G5" t="n">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="6">
@@ -752,16 +752,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="G8" t="n">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="9">
@@ -781,16 +781,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="G9" t="n">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
   </sheetData>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7853</v>
+        <v>7859</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9224</v>
+        <v>9230</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1193,13 +1193,13 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>43534</v>
       </c>
       <c r="F2" t="n">
-        <v>2624</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="3">
@@ -1219,13 +1219,13 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46162</v>
+        <v>46165</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>36596</v>
       </c>
       <c r="F3" t="n">
-        <v>2592</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="4">
@@ -1245,13 +1245,13 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46162</v>
+        <v>46165</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>37951</v>
       </c>
       <c r="F4" t="n">
-        <v>2287</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="5">
@@ -1271,13 +1271,13 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46162</v>
+        <v>46165</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>42949</v>
       </c>
       <c r="F5" t="n">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="6">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="F8" t="n">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="9">
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="F9" t="n">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/quality/lottery_quality_report.xlsx
+++ b/data/processed/quality/lottery_quality_report.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12709</v>
+        <v>12713</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:04</t>
+          <t>2026-05-25 14:23:59</t>
         </is>
       </c>
     </row>
@@ -578,16 +578,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2625</v>
+        <v>2626</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>43534</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="G2" t="n">
-        <v>2625</v>
+        <v>2626</v>
       </c>
     </row>
     <row r="3">
@@ -752,16 +752,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="G8" t="n">
-        <v>736</v>
+        <v>738</v>
       </c>
     </row>
     <row r="9">
@@ -781,16 +781,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="G9" t="n">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
   </sheetData>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7859</v>
+        <v>7863</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9230</v>
+        <v>9234</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1193,13 +1193,13 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>43534</v>
       </c>
       <c r="F2" t="n">
-        <v>2625</v>
+        <v>2626</v>
       </c>
     </row>
     <row r="3">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="F8" t="n">
-        <v>736</v>
+        <v>738</v>
       </c>
     </row>
     <row r="9">
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="F9" t="n">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/quality/lottery_quality_report.xlsx
+++ b/data/processed/quality/lottery_quality_report.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12713</v>
+        <v>12716</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-25 14:23:59</t>
+          <t>2026-05-26 14:14:48</t>
         </is>
       </c>
     </row>
@@ -578,16 +578,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2626</v>
+        <v>2627</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>43534</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="G2" t="n">
-        <v>2626</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="3">
@@ -752,16 +752,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="G8" t="n">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="9">
@@ -781,16 +781,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="G9" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
   </sheetData>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7863</v>
+        <v>7866</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9234</v>
+        <v>9237</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1193,13 +1193,13 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>43534</v>
       </c>
       <c r="F2" t="n">
-        <v>2626</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="3">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="F8" t="n">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="9">
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="F9" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/quality/lottery_quality_report.xlsx
+++ b/data/processed/quality/lottery_quality_report.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12716</v>
+        <v>12721</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-26 14:14:48</t>
+          <t>2026-05-27 14:48:18</t>
         </is>
       </c>
     </row>
@@ -578,16 +578,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2627</v>
+        <v>2628</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>43534</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="G2" t="n">
-        <v>2627</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="3">
@@ -694,16 +694,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>40109</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="G6" t="n">
-        <v>1722</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="7">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>42339</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="G7" t="n">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="8">
@@ -752,16 +752,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="G8" t="n">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="9">
@@ -781,16 +781,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="G9" t="n">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
   </sheetData>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7866</v>
+        <v>7871</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9237</v>
+        <v>9242</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1193,13 +1193,13 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>43534</v>
       </c>
       <c r="F2" t="n">
-        <v>2627</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="3">
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>40109</v>
       </c>
       <c r="F6" t="n">
-        <v>1722</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="7">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>42339</v>
       </c>
       <c r="F7" t="n">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="8">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="F8" t="n">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="9">
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="F9" t="n">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/quality/lottery_quality_report.xlsx
+++ b/data/processed/quality/lottery_quality_report.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-27 14:48:18</t>
+          <t>2026-05-28 08:46:33</t>
         </is>
       </c>
     </row>

--- a/data/processed/quality/lottery_quality_report.xlsx
+++ b/data/processed/quality/lottery_quality_report.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12721</v>
+        <v>12728</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-28 08:46:33</t>
+          <t>2026-05-28 17:12:22</t>
         </is>
       </c>
     </row>
@@ -578,16 +578,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2628</v>
+        <v>2629</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>43534</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="G2" t="n">
-        <v>2628</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="3">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2593</v>
+        <v>2594</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>36596</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>46165</v>
+        <v>46169</v>
       </c>
       <c r="G3" t="n">
-        <v>2593</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="4">
@@ -636,16 +636,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>37951</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>46165</v>
+        <v>46169</v>
       </c>
       <c r="G4" t="n">
-        <v>2288</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="5">
@@ -665,16 +665,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>42949</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46165</v>
+        <v>46169</v>
       </c>
       <c r="G5" t="n">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="6">
@@ -752,16 +752,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="G8" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="9">
@@ -781,16 +781,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="G9" t="n">
-        <v>739</v>
+        <v>741</v>
       </c>
     </row>
   </sheetData>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7871</v>
+        <v>7878</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9242</v>
+        <v>9249</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1193,13 +1193,13 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>43534</v>
       </c>
       <c r="F2" t="n">
-        <v>2628</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="3">
@@ -1219,13 +1219,13 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46165</v>
+        <v>46169</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>36596</v>
       </c>
       <c r="F3" t="n">
-        <v>2593</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="4">
@@ -1245,13 +1245,13 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46165</v>
+        <v>46169</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>37951</v>
       </c>
       <c r="F4" t="n">
-        <v>2288</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="5">
@@ -1271,13 +1271,13 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46165</v>
+        <v>46169</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>42949</v>
       </c>
       <c r="F5" t="n">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="6">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="F8" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="9">
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="F9" t="n">
-        <v>739</v>
+        <v>741</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/quality/lottery_quality_report.xlsx
+++ b/data/processed/quality/lottery_quality_report.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-28 17:12:22</t>
+          <t>2026-05-28 19:42:06</t>
         </is>
       </c>
     </row>
